--- a/logs/multi_port_transactions.xlsx
+++ b/logs/multi_port_transactions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,68 +484,64 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>马峙</t>
+          <t>秀山东</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>马峙; 虾峙门</t>
+          <t>秀山东; 虾峙门</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>虾峙门</t>
+          <t>马峙</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>虾峙门; 条帚门</t>
+          <t>马峙; 虾峙门</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>283</v>
+        <v>244</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>秀山东</t>
+          <t>虾峙门</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>秀山东; 虾峙门</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>At Zhoushan Xiazhimen Kou</t>
-        </is>
-      </c>
+          <t>虾峙门; 条帚门</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>309</v>
+        <v>283</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>马峙</t>
+          <t>秀山东</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>马峙; 条帚门</t>
+          <t>秀山东; 虾峙门</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -556,23 +552,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>332</v>
+        <v>309</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>秀山东</t>
+          <t>马峙</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>秀山东; 条帚门</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>马峙; 条帚门</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>At Zhoushan Xiazhimen Kou</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -581,30 +581,30 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>秀山东; 虾峙门</t>
+          <t>秀山东; 条帚门</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>449</v>
+        <v>352</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>条帚门</t>
+          <t>秀山东</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>条帚门; 虾峙门</t>
+          <t>秀山东; 虾峙门</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>643</v>
+        <v>449</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -613,18 +613,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>条帚门; 秀山东</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>At Zhoushan Xiazhimen Kouwai Tanker Anchorage</t>
-        </is>
-      </c>
+          <t>条帚门; 虾峙门</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>714</v>
+        <v>535</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -633,50 +629,50 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>虾峙门; 条帚门</t>
+          <t>虾峙门; 秀山东</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>753</v>
+        <v>643</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>虾峙门</t>
+          <t>条帚门</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>虾峙门; 衢山</t>
+          <t>条帚门; 秀山东</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>At Zhoushan Xiazhimen Kou Ore Carrier Anchorage</t>
+          <t>At Zhoushan Xiazhimen Kouwai Tanker Anchorage</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>785</v>
+        <v>714</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>秀山东</t>
+          <t>虾峙门</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>秀山东; 条帚门</t>
+          <t>虾峙门; 条帚门</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>810</v>
+        <v>753</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -685,14 +681,18 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>虾峙门; 条帚门</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>虾峙门; 衢山</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>At Zhoushan Xiazhimen Kou Ore Carrier Anchorage</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>838</v>
+        <v>785</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -708,63 +708,59 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>875</v>
+        <v>810</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>秀山东</t>
+          <t>虾峙门</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>秀山东; 虾峙门</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>At Zhoushan Xiazhimen Kou Ore Carrier Anchorage; At Zhoushan Xiazhimen Kou</t>
-        </is>
-      </c>
+          <t>虾峙门; 条帚门</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>959</v>
+        <v>838</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>马峙</t>
+          <t>秀山东</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>马峙; 条帚门</t>
+          <t>秀山东; 条帚门</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>983</v>
+        <v>875</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>马峙</t>
+          <t>秀山东</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>马峙; 虾峙门</t>
+          <t>秀山东; 虾峙门</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>At Zhoushan Xiazhimen Kou</t>
+          <t>At Zhoushan Xiazhimen Kou Ore Carrier Anchorage; At Zhoushan Xiazhimen Kou</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1029</v>
+        <v>959</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -780,7 +776,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1140</v>
+        <v>983</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -794,13 +790,13 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>At Zhoushan Xiazhimen Kou Ore Carrier Anchorage; At Zhoushan Xiazhime</t>
+          <t>At Zhoushan Xiazhimen Kou</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1294</v>
+        <v>1029</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -809,94 +805,162 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>马峙; 虾峙门</t>
+          <t>马峙; 条帚门</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1508</v>
+        <v>1140</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>条帚门</t>
+          <t>马峙</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>条帚门; 虾峙门</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>马峙; 虾峙门</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>At Zhoushan Xiazhimen Kou Ore Carrier Anchorage; At Zhoushan Xiazhime</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1558</v>
+        <v>1294</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>秀山东</t>
+          <t>马峙</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>秀山东; 条帚门</t>
+          <t>马峙; 虾峙门</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1590</v>
+        <v>1321</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>条帚门</t>
+          <t>秀山东</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>条帚门; 虾峙门</t>
+          <t>秀山东; 虾峙门</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1596</v>
+        <v>1343</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>虾峙门</t>
+          <t>马峙</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>虾峙门; 马峙</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>At Zhoushan Xiazhimen Kouwai Tanker Anchorage</t>
-        </is>
-      </c>
+          <t>马峙; 秀山东</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
+        <v>1508</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>条帚门</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>条帚门; 虾峙门</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1558</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>秀山东</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>秀山东; 条帚门</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1590</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>条帚门</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>条帚门; 虾峙门</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1596</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>虾峙门</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>虾峙门; 马峙</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>At Zhoushan Xiazhimen Kouwai Tanker Anchorage</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
         <v>1601</v>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>秀山东</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>秀山东</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>秀山东; 虾峙门</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/logs/multi_port_transactions.xlsx
+++ b/logs/multi_port_transactions.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,68 +484,64 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>马峙</t>
+          <t>秀山东</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>马峙; 虾峙门</t>
+          <t>秀山东; 虾峙门</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>虾峙门</t>
+          <t>马峙</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>虾峙门; 条帚门</t>
+          <t>马峙; 虾峙门</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>283</v>
+        <v>244</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>秀山东</t>
+          <t>虾峙门</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>秀山东; 虾峙门</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>At Zhoushan Xiazhimen Kou</t>
-        </is>
-      </c>
+          <t>虾峙门; 条帚门</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>309</v>
+        <v>283</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>马峙</t>
+          <t>秀山东</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>马峙; 条帚门</t>
+          <t>秀山东; 虾峙门</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -556,23 +552,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>332</v>
+        <v>309</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>秀山东</t>
+          <t>马峙</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>秀山东; 条帚门</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>马峙; 条帚门</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>At Zhoushan Xiazhimen Kou</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -581,30 +581,30 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>秀山东; 虾峙门</t>
+          <t>秀山东; 条帚门</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>449</v>
+        <v>352</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>条帚门</t>
+          <t>秀山东</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>条帚门; 虾峙门</t>
+          <t>秀山东; 虾峙门</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>643</v>
+        <v>449</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -613,18 +613,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>条帚门; 秀山东</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>At Zhoushan Xiazhimen Kouwai Tanker Anchorage</t>
-        </is>
-      </c>
+          <t>条帚门; 虾峙门</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>714</v>
+        <v>535</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -633,50 +629,50 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>虾峙门; 条帚门</t>
+          <t>虾峙门; 秀山东</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>753</v>
+        <v>643</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>虾峙门</t>
+          <t>条帚门</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>虾峙门; 衢山</t>
+          <t>条帚门; 秀山东</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>At Zhoushan Xiazhimen Kou Ore Carrier Anchorage</t>
+          <t>At Zhoushan Xiazhimen Kouwai Tanker Anchorage</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>785</v>
+        <v>714</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>秀山东</t>
+          <t>虾峙门</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>秀山东; 条帚门</t>
+          <t>虾峙门; 条帚门</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>810</v>
+        <v>753</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -685,14 +681,18 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>虾峙门; 条帚门</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>虾峙门; 衢山</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>At Zhoushan Xiazhimen Kou Ore Carrier Anchorage</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>838</v>
+        <v>785</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -708,63 +708,59 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>875</v>
+        <v>810</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>秀山东</t>
+          <t>虾峙门</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>秀山东; 虾峙门</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>At Zhoushan Xiazhimen Kou Ore Carrier Anchorage; At Zhoushan Xiazhimen Kou</t>
-        </is>
-      </c>
+          <t>虾峙门; 条帚门</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>959</v>
+        <v>838</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>马峙</t>
+          <t>秀山东</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>马峙; 条帚门</t>
+          <t>秀山东; 条帚门</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>983</v>
+        <v>875</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>马峙</t>
+          <t>秀山东</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>马峙; 虾峙门</t>
+          <t>秀山东; 虾峙门</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>At Zhoushan Xiazhimen Kou</t>
+          <t>At Zhoushan Xiazhimen Kou Ore Carrier Anchorage; At Zhoushan Xiazhimen Kou</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1029</v>
+        <v>959</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -780,7 +776,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1140</v>
+        <v>983</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -794,13 +790,13 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>At Zhoushan Xiazhimen Kou Ore Carrier Anchorage; At Zhoushan Xiazhime</t>
+          <t>At Zhoushan Xiazhimen Kou</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1294</v>
+        <v>1029</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -809,94 +805,162 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>马峙; 虾峙门</t>
+          <t>马峙; 条帚门</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1508</v>
+        <v>1140</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>条帚门</t>
+          <t>马峙</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>条帚门; 虾峙门</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>马峙; 虾峙门</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>At Zhoushan Xiazhimen Kou Ore Carrier Anchorage; At Zhoushan Xiazhime</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1558</v>
+        <v>1294</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>秀山东</t>
+          <t>马峙</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>秀山东; 条帚门</t>
+          <t>马峙; 虾峙门</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1590</v>
+        <v>1321</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>条帚门</t>
+          <t>秀山东</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>条帚门; 虾峙门</t>
+          <t>秀山东; 虾峙门</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1596</v>
+        <v>1343</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>虾峙门</t>
+          <t>马峙</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>虾峙门; 马峙</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>At Zhoushan Xiazhimen Kouwai Tanker Anchorage</t>
-        </is>
-      </c>
+          <t>马峙; 秀山东</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
+        <v>1508</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>条帚门</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>条帚门; 虾峙门</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>1558</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>秀山东</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>秀山东; 条帚门</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>1590</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>条帚门</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>条帚门; 虾峙门</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>1596</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>虾峙门</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>虾峙门; 马峙</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>At Zhoushan Xiazhimen Kouwai Tanker Anchorage</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
         <v>1601</v>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>秀山东</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>秀山东</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>秀山东; 虾峙门</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
